--- a/reports/pdf_change_20260825.xlsx
+++ b/reports/pdf_change_20260825.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,20 +38,37 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -58,16 +77,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00DCE6F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F2"/>
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,11 +114,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -90,10 +143,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 1/7  ·  대기: KoAct, KoAct, TIME, TIME, PLUS, TIGER</t>
+          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 33억(0.7%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -506,93 +588,345 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>아이티센글로벌  (신규)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>2300946900</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.52%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>0→59</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-45</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-3477505500</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>0.94%→0.12%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>52→7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>888644400</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2.75%→2.69%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>420→454</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>코세스  (편출)</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-431099550</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.10%→0.00%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>19→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>894766950</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.62%→1.90%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>276→309</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-857980200</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>1.67%→1.47%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>94→83</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>티씨케이  (신규)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>2106877500</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.48%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-866006400</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>4.24%→4.21%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>180→172</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>989383500</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>7.11%→7.24%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>94→97</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>고영</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-196281750</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.55%→0.48%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>83→76</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-398840400</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>5.77%→5.51%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>372→366</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 19억(0.5%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -601,7 +935,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억   ·   현금 37억(1.5%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -615,18 +949,112 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
     </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억   ·   현금 28억(1.2%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="20" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="15">
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A19:K19"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260825.xlsx
+++ b/reports/pdf_change_20260825.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 33억(0.7%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 5종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -911,7 +911,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 19억(0.5%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -935,7 +935,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억   ·   현금 37억(1.5%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -959,7 +959,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억   ·   현금 28억(1.2%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -981,80 +981,342 @@
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.5%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 3종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>97088000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>3.17%→3.54%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>697→777</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-71</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-45184400</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>7.27%→7.12%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>3,052→2,981</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>42328000</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.03%→1.19%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>104→120</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-77892400</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>3.03%→2.75%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>395→357</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>54545400</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>1.02%→1.23%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>35→42</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-84304500</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>3.02%→2.71%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>335→300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-31</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>-25142240</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>2.75%→2.67%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>907→876</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-23665200</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>0.28%→0.19%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>19→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="20" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:K32"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A14:K14"/>
+    <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260825.xlsx
+++ b/reports/pdf_change_20260825.xlsx
@@ -983,7 +983,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.5%)      당일 2026-08-25  vs  전영업일 2026-08-24      매수 3종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>

--- a/reports/pdf_change_20260825.xlsx
+++ b/reports/pdf_change_20260825.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 5종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>59</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2300946900</v>
+        <v>2303183000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-45</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3477505500</v>
+        <v>-3480885000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>34</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>888644400</v>
+        <v>889508000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-19</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-431099550</v>
+        <v>-431518500</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>894766950</v>
+        <v>895636500</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-11</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-857980200</v>
+        <v>-858814000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2106877500</v>
+        <v>2108925000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-8</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-866006400</v>
+        <v>-866848000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>989383500</v>
+        <v>990345000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-7</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-196281750</v>
+        <v>-196472500</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>-6</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-398840400</v>
+        <v>-399228000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -935,7 +935,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -959,7 +959,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -983,7 +983,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 3종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1079,11 +1079,11 @@
         <v>80</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>97088000</v>
+        <v>98568000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>3.17%→3.54%</t>
+          <t>3.15%→3.52%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1100,11 +1100,11 @@
         <v>-71</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-45184400</v>
+        <v>-47338540</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>7.27%→7.12%</t>
+          <t>7.45%→7.30%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
@@ -1123,11 +1123,11 @@
         <v>16</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>42328000</v>
+        <v>41558400</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.19%</t>
+          <t>0.99%→1.14%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1144,11 +1144,11 @@
         <v>-38</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-77892400</v>
+        <v>-71424800</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>3.03%→2.75%</t>
+          <t>2.72%→2.46%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
@@ -1167,11 +1167,11 @@
         <v>7</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>54545400</v>
+        <v>54182800</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.23%</t>
+          <t>0.99%→1.19%</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1188,11 +1188,11 @@
         <v>-35</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-84304500</v>
+        <v>-93758000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>3.02%→2.71%</t>
+          <t>3.29%→2.95%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1216,11 +1216,11 @@
         <v>-31</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-25142240</v>
+        <v>-27940920</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.75%→2.67%</t>
+          <t>2.99%→2.90%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1244,11 +1244,11 @@
         <v>-6</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-23665200</v>
+        <v>-25441200</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.19%</t>
+          <t>0.30%→0.20%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1260,7 +1260,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억      당일 2026-08-25  vs  전영업일 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
